--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434229</v>
+        <v>121433920</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520190</v>
+        <v>519955</v>
       </c>
       <c r="R2" t="n">
-        <v>6996102</v>
+        <v>6996084</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121433920</v>
+        <v>121434229</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519955</v>
+        <v>520190</v>
       </c>
       <c r="R5" t="n">
-        <v>6996084</v>
+        <v>6996102</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121433920</v>
+        <v>121434229</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519955</v>
+        <v>520190</v>
       </c>
       <c r="R2" t="n">
-        <v>6996084</v>
+        <v>6996102</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>121433931</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121434088</v>
+        <v>121433920</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520068</v>
+        <v>519955</v>
       </c>
       <c r="R4" t="n">
-        <v>6996127</v>
+        <v>6996084</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121434229</v>
+        <v>121434088</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520190</v>
+        <v>520068</v>
       </c>
       <c r="R5" t="n">
-        <v>6996102</v>
+        <v>6996127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434229</v>
+        <v>121433920</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520190</v>
+        <v>519955</v>
       </c>
       <c r="R2" t="n">
-        <v>6996102</v>
+        <v>6996084</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121433920</v>
+        <v>121434229</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519955</v>
+        <v>520190</v>
       </c>
       <c r="R4" t="n">
-        <v>6996084</v>
+        <v>6996102</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121433920</v>
+        <v>121434229</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519955</v>
+        <v>520190</v>
       </c>
       <c r="R2" t="n">
-        <v>6996084</v>
+        <v>6996102</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>121433931</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121434229</v>
+        <v>121433920</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520190</v>
+        <v>519955</v>
       </c>
       <c r="R4" t="n">
-        <v>6996102</v>
+        <v>6996084</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>121434088</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434229</v>
+        <v>121434088</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520190</v>
+        <v>520068</v>
       </c>
       <c r="R2" t="n">
-        <v>6996102</v>
+        <v>6996127</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121434088</v>
+        <v>121434229</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520068</v>
+        <v>520190</v>
       </c>
       <c r="R5" t="n">
-        <v>6996127</v>
+        <v>6996102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434088</v>
+        <v>121433931</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520068</v>
+        <v>519957</v>
       </c>
       <c r="R2" t="n">
-        <v>6996127</v>
+        <v>6996080</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121433931</v>
+        <v>121433920</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519957</v>
+        <v>519955</v>
       </c>
       <c r="R3" t="n">
-        <v>6996080</v>
+        <v>6996084</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121433920</v>
+        <v>121434088</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519955</v>
+        <v>520068</v>
       </c>
       <c r="R4" t="n">
-        <v>6996084</v>
+        <v>6996127</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>121434229</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121433931</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121433920</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121434088</v>
+        <v>121434229</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520068</v>
+        <v>520190</v>
       </c>
       <c r="R4" t="n">
-        <v>6996127</v>
+        <v>6996102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121434229</v>
+        <v>121434088</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520190</v>
+        <v>520068</v>
       </c>
       <c r="R5" t="n">
-        <v>6996102</v>
+        <v>6996127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121433931</v>
+        <v>121434229</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519957</v>
+        <v>520190</v>
       </c>
       <c r="R2" t="n">
-        <v>6996080</v>
+        <v>6996102</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121434229</v>
+        <v>121434088</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520190</v>
+        <v>520068</v>
       </c>
       <c r="R4" t="n">
-        <v>6996102</v>
+        <v>6996127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121434088</v>
+        <v>121433931</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520068</v>
+        <v>519957</v>
       </c>
       <c r="R5" t="n">
-        <v>6996127</v>
+        <v>6996080</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434229</v>
+        <v>121433920</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520190</v>
+        <v>519955</v>
       </c>
       <c r="R2" t="n">
-        <v>6996102</v>
+        <v>6996084</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121433920</v>
+        <v>121434229</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519955</v>
+        <v>520190</v>
       </c>
       <c r="R3" t="n">
-        <v>6996084</v>
+        <v>6996102</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121434088</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>121433931</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54967-2024 artfynd.xlsx
+++ b/artfynd/A 54967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121433920</v>
+        <v>121433931</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519955</v>
+        <v>519957</v>
       </c>
       <c r="R2" t="n">
-        <v>6996084</v>
+        <v>6996080</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121434229</v>
+        <v>121434088</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
+          <t>Stockflon, Stockflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520190</v>
+        <v>520068</v>
       </c>
       <c r="R3" t="n">
-        <v>6996102</v>
+        <v>6996127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121434088</v>
+        <v>121434229</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stockflon, Stockflon, Jmt</t>
+          <t>Gårdstjärnhöjden, Gårdstjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520068</v>
+        <v>520190</v>
       </c>
       <c r="R4" t="n">
-        <v>6996127</v>
+        <v>6996102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121433931</v>
+        <v>121433920</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519957</v>
+        <v>519955</v>
       </c>
       <c r="R5" t="n">
-        <v>6996080</v>
+        <v>6996084</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
